--- a/docs/oc-regiones/alimentos/coquimbo.xlsx
+++ b/docs/oc-regiones/alimentos/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M547"/>
+  <dimension ref="A1:M551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1561.74</v>
+        <v>1545.38</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1083.68</v>
+        <v>1072.34</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2997.21</v>
+        <v>2980.83</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4664.65</v>
+        <v>4639.15</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1193.55</v>
+        <v>1187.02</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3533.72</v>
+        <v>3514.4</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1742.29</v>
+        <v>1732.77</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1065.04</v>
+        <v>1059.22</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1118.09</v>
+        <v>1111.98</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6687.5</v>
+        <v>6650.95</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3957.48</v>
+        <v>3935.84</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3284.33</v>
+        <v>3247.74</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3131.51</v>
+        <v>3114.36</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13781.38</v>
+        <v>13705.9</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3549</v>
+        <v>3529.56</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1262.97</v>
+        <v>1256.05</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>762.02</v>
+        <v>757.84</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2659.22</v>
+        <v>2644.66</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2101.71</v>
+        <v>2090.2</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1334.11</v>
+        <v>1326.8</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3119.51</v>
+        <v>3102.42</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>764.03</v>
+        <v>763.0599999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2347.68</v>
+        <v>2344.69</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1951.17</v>
+        <v>1948.69</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4089.29</v>
+        <v>4103.89</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2837.61</v>
+        <v>2847.73</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>30534.24</v>
+        <v>30866.34</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13317.12</v>
+        <v>13461.97</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6008.63</v>
+        <v>6073.98</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3037.92</v>
+        <v>3047.91</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1504.24</v>
+        <v>1509.18</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2071.05</v>
+        <v>2077.87</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2700.88</v>
+        <v>2709.76</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4748.97</v>
+        <v>4830.95</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2324.78</v>
+        <v>2364.91</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1830.46</v>
+        <v>1862.06</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8490</v>
+        <v>8636.549999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1202.76</v>
+        <v>1223.52</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>987.5</v>
+        <v>1004.55</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2668.03</v>
+        <v>2714.08</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1830.95</v>
+        <v>1862.56</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1254.48</v>
+        <v>1276.14</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1370.69</v>
+        <v>1380.18</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>811.21</v>
+        <v>817.0599999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1573.63</v>
+        <v>1570.84</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2885.71</v>
+        <v>2880.6</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2633.09</v>
+        <v>2628.42</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3877.21</v>
+        <v>3870.34</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1775.8</v>
+        <v>1772.65</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1106.91</v>
+        <v>1102.35</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2986.46</v>
+        <v>2974.15</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1118.14</v>
+        <v>1113.53</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1993.1</v>
+        <v>1990.01</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2853.21</v>
+        <v>2848.79</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8159.29</v>
+        <v>8146.64</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2610.78</v>
+        <v>2606.73</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2530.77</v>
+        <v>2526.84</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2464.01</v>
+        <v>2460.19</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1469.06</v>
+        <v>1466.79</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2273.86</v>
+        <v>2270.34</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>786.3099999999999</v>
+        <v>785.1</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>17529.93</v>
+        <v>17620.46</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4744.72</v>
+        <v>4769.22</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2801.58</v>
+        <v>2816.04</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2801.58</v>
+        <v>2816.04</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>938.08</v>
+        <v>944.7</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3481.69</v>
+        <v>3436.69</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4023.7</v>
+        <v>3971.69</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1120.07</v>
+        <v>1105.59</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1022.52</v>
+        <v>1009.31</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>823.08</v>
+        <v>812.4400000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1170.26</v>
+        <v>1155.13</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>891.91</v>
+        <v>880.58</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2746.11</v>
+        <v>2718.79</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2695.76</v>
+        <v>2668.94</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1901.28</v>
+        <v>1882.36</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>778.3200000000001</v>
+        <v>775.53</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1002.22</v>
+        <v>998.62</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3359.66</v>
+        <v>3352.39</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3354.36</v>
+        <v>3340.3</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>780.0700000000001</v>
+        <v>776.8</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>773.12</v>
+        <v>764.17</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1168.86</v>
+        <v>1158.96</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10571.96</v>
+        <v>10619.87</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7514.38</v>
+        <v>7503.84</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>11107.54</v>
+        <v>11091.96</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1180.92</v>
+        <v>1179.26</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1120.92</v>
+        <v>1122.36</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8513.51</v>
+        <v>8572.110000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>764.51</v>
+        <v>772.71</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>908.36</v>
+        <v>885.16</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3920.55</v>
+        <v>3844.08</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>912.52</v>
+        <v>891.1799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1151.74</v>
+        <v>1124.8</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>873.29</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1153.37</v>
+        <v>1126.39</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5820.53</v>
+        <v>5684.37</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1222.7</v>
+        <v>1194.1</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>928.54</v>
+        <v>906.8200000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>10735.9</v>
+        <v>10484.75</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3771.16</v>
+        <v>3682.94</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2190.02</v>
+        <v>2138.79</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4510.35</v>
+        <v>4404.84</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5876.73</v>
+        <v>5792.5</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1634.6</v>
+        <v>1611.17</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>854.5</v>
+        <v>842.26</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1960.6</v>
+        <v>1932.5</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>11935.17</v>
+        <v>11764.1</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1425.26</v>
+        <v>1404.83</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2565.57</v>
+        <v>2533.01</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2433.35</v>
+        <v>2402.47</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2317.72</v>
+        <v>2288.3</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1409.81</v>
+        <v>1391.92</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3179.78</v>
+        <v>3139.42</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>831.23</v>
+        <v>820.6799999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>941.27</v>
+        <v>927.71</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2871.72</v>
+        <v>2830.34</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>823.5599999999999</v>
+        <v>811.6900000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1198.36</v>
+        <v>1181.09</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3061.11</v>
+        <v>3021.54</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3061.11</v>
+        <v>3021.54</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3061.11</v>
+        <v>3021.54</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1201.47</v>
+        <v>1199.1</v>
       </c>
     </row>
     <row r="125">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4270.96</v>
+        <v>4268.04</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7855.96</v>
+        <v>7814.46</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>14442.64</v>
+        <v>14366.35</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3712.81</v>
+        <v>3693.2</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>911.53</v>
+        <v>906.71</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>793.84</v>
+        <v>789.65</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3200.9</v>
+        <v>3180.84</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5671.17</v>
+        <v>5635.63</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3870.46</v>
+        <v>3895.83</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1009.24</v>
+        <v>1015.85</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1317.02</v>
+        <v>1325.65</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1545.15</v>
+        <v>1565.96</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3054.87</v>
+        <v>3101.37</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>13486.67</v>
+        <v>13814.63</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1216.68</v>
+        <v>1246.26</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1319.96</v>
+        <v>1352.06</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>792.09</v>
+        <v>811.35</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>790.85</v>
+        <v>810.09</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1300.24</v>
+        <v>1331.86</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>810.72</v>
+        <v>830.4299999999999</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1542.21</v>
+        <v>1579.71</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1819.96</v>
+        <v>1864.21</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3747.53</v>
+        <v>3838.66</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1622.01</v>
+        <v>1663.01</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2098.53</v>
+        <v>2151.58</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1088.02</v>
+        <v>1115.53</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>7389.15</v>
+        <v>7575.95</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2732.56</v>
+        <v>2801.64</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>797.45</v>
+        <v>817.61</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1074.14</v>
+        <v>1101.3</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>24877.89</v>
+        <v>25632.26</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1979.52</v>
+        <v>2039.55</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5226.84</v>
+        <v>5385.33</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2414.37</v>
+        <v>2487.59</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2888.78</v>
+        <v>2976.38</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>873.85</v>
+        <v>900.34</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1250.7</v>
+        <v>1287.88</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3870.77</v>
+        <v>3985.82</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>935.87</v>
+        <v>963.6900000000001</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2724.27</v>
+        <v>2805.24</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6434.01</v>
+        <v>6625.25</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2433.82</v>
+        <v>2506.16</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>912.52</v>
+        <v>939.65</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1438.36</v>
+        <v>1481.11</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7587.29</v>
+        <v>7560.28</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5048.1</v>
+        <v>5062.72</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>11319.29</v>
+        <v>11352.08</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1046.2</v>
+        <v>1049.23</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1410.5</v>
+        <v>1417.78</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>825.66</v>
+        <v>829.9299999999999</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3065.5</v>
+        <v>3052.57</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3065.5</v>
+        <v>3052.57</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3065.5</v>
+        <v>3052.57</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1121.61</v>
+        <v>1116.88</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>817.08</v>
+        <v>813.64</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2245.77</v>
+        <v>2236.3</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1549.73</v>
+        <v>1543.19</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1969.62</v>
+        <v>1961.31</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>904.85</v>
+        <v>901.04</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3058.56</v>
+        <v>3045.66</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>16359.2</v>
+        <v>16290.22</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>886.38</v>
+        <v>894.4400000000001</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2795.06</v>
+        <v>2820.49</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1808.22</v>
+        <v>1824.66</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1438.56</v>
+        <v>1451.64</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3068.84</v>
+        <v>3096.75</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1109.21</v>
+        <v>1119.3</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1774.49</v>
+        <v>1786.18</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4527.16</v>
+        <v>4556.97</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7381.73</v>
+        <v>7430.35</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>7891.23</v>
+        <v>7943.2</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1386.33</v>
+        <v>1395.46</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1229.67</v>
+        <v>1227.56</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2241.17</v>
+        <v>2237.32</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1377.89</v>
+        <v>1375.53</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>9258.42</v>
+        <v>9192.09</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2971.51</v>
+        <v>2967.14</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>858.22</v>
+        <v>853.16</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1071.48</v>
+        <v>1064.97</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>855.46</v>
+        <v>852.15</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1029.38</v>
+        <v>1025.41</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6807.58</v>
+        <v>6781.3</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>20691.7</v>
+        <v>20611.84</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1317.58</v>
+        <v>1324.4</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3433.84</v>
+        <v>3451.62</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>820.8200000000001</v>
+        <v>825.0700000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>920.63</v>
+        <v>925.39</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4674.42</v>
+        <v>4698.62</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3045.73</v>
+        <v>3048.67</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1348.29</v>
+        <v>1349.59</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1261.51</v>
+        <v>1262.73</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1567.34</v>
+        <v>1612.87</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>19320.07</v>
+        <v>19396.24</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>783.13</v>
+        <v>796.04</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1392.81</v>
+        <v>1396.24</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2061.04</v>
+        <v>2066.11</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2067.03</v>
+        <v>2072.12</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2342.33</v>
+        <v>2348.09</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1431.13</v>
+        <v>1434.66</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>783.53</v>
+        <v>785.46</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1384.14</v>
+        <v>1387.55</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>798.62</v>
+        <v>800.59</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3596.95</v>
+        <v>3605.8</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7550.17</v>
+        <v>7568.75</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2633.59</v>
+        <v>2640.07</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2166.57</v>
+        <v>2171.9</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1270.13</v>
+        <v>1273.25</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6041.04</v>
+        <v>6055.9</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>794.3099999999999</v>
+        <v>784.08</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2440.78</v>
+        <v>2423.55</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>793.67</v>
+        <v>788.0700000000001</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1218.42</v>
+        <v>1209.82</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1669.25</v>
+        <v>1657.47</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1120.85</v>
+        <v>1141.17</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2267.08</v>
+        <v>2266.96</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3441</v>
+        <v>3440.82</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8448.639999999999</v>
+        <v>8448.209999999999</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>777.52</v>
+        <v>777.48</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3243.35</v>
+        <v>3228.85</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2818.68</v>
+        <v>2806.08</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>8475.059999999999</v>
+        <v>8437.16</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1182.01</v>
+        <v>1183.03</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1165.06</v>
+        <v>1166.06</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2128.98</v>
+        <v>2130.81</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1545.96</v>
+        <v>1547.29</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2703.83</v>
+        <v>2706.16</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>777.45</v>
+        <v>780.66</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1279.17</v>
+        <v>1284.46</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2905.66</v>
+        <v>2917.66</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6591.74</v>
+        <v>6618.97</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7285.12</v>
+        <v>7265.02</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1863.3</v>
+        <v>1835.51</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2563.16</v>
+        <v>2524.93</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>14017.91</v>
+        <v>13808.83</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>858.53</v>
+        <v>853.6</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>785.76</v>
+        <v>780.73</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>781.09</v>
+        <v>777.73</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3043.51</v>
+        <v>2999.48</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1083.03</v>
+        <v>1067.36</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>811.15</v>
+        <v>799.41</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>7516.49</v>
+        <v>7354.77</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>9950.92</v>
+        <v>9736.82</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1072.71</v>
+        <v>1049.63</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1505.01</v>
+        <v>1472.63</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1691.11</v>
+        <v>1651.76</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1050.63</v>
+        <v>1026.19</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>780.45</v>
+        <v>755.5700000000001</v>
       </c>
     </row>
     <row r="273">
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2013.62</v>
+        <v>1949.41</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>627786-64-CM26</t>
+          <t>627786-63-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17146,12 +17146,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRIO SUR ALIMENTOS DEL MAR S.A </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>78.081.820-4</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2521.25</v>
+        <v>3618.55</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>627786-62-CM26</t>
+          <t>627786-64-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t xml:space="preserve">FRIO SUR ALIMENTOS DEL MAR S.A </t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>78.081.820-4</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17222,13 +17222,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>7907.59</v>
+        <v>2440.86</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>627786-63-CM26</t>
+          <t>627786-62-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17268,12 +17268,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3737.73</v>
+        <v>7655.44</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2408.02</v>
+        <v>2331.24</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>966</v>
+        <v>935.1900000000001</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7008.38</v>
+        <v>6870.16</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1042.94</v>
+        <v>1022.37</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1303.92</v>
+        <v>1278.21</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4398.82</v>
+        <v>4312.07</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1176.8</v>
+        <v>1153.59</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2003.87</v>
+        <v>1951.1</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>796.27</v>
+        <v>775.3</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2738.18</v>
+        <v>2666.07</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1123.3</v>
+        <v>1093.72</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1614.93</v>
+        <v>1585.64</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1725.29</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>804.66</v>
+        <v>783.12</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2167.42</v>
+        <v>2109.39</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1049.46</v>
+        <v>1021.36</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>791.41</v>
+        <v>770.22</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>785.62</v>
+        <v>764.59</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>975.39</v>
+        <v>949.27</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1083.67</v>
+        <v>1054.65</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2269.26</v>
+        <v>2208.5</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1216.14</v>
+        <v>1183.58</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2546.46</v>
+        <v>2478.27</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1239.8</v>
+        <v>1206.6</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>19828.79</v>
+        <v>19297.85</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4740.64</v>
+        <v>4613.7</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1130.66</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>3135.01</v>
+        <v>3144.13</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3135.01</v>
+        <v>3144.13</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3135.01</v>
+        <v>3144.13</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2358.27</v>
+        <v>2368.07</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>5939.36</v>
+        <v>5964.04</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1510.88</v>
+        <v>1517.16</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2429.93</v>
+        <v>2440.03</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2411.32</v>
+        <v>2421.34</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>6706.08</v>
+        <v>6733.95</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1313.31</v>
+        <v>1318.76</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2690.43</v>
+        <v>2713.27</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>779.34</v>
+        <v>785.95</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3172.79</v>
+        <v>3199.71</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>865.36</v>
+        <v>876.88</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2427.92</v>
+        <v>2459.61</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>6344.31</v>
+        <v>6427.1</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>849.99</v>
+        <v>861.09</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2263.97</v>
+        <v>2293.52</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2453.54</v>
+        <v>2513.92</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>916.99</v>
+        <v>934.33</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1195.59</v>
+        <v>1218.2</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1277.38</v>
+        <v>1301.54</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>5006.43</v>
+        <v>5063.36</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>793.27</v>
+        <v>800.41</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>784.0599999999999</v>
+        <v>791.13</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2759.09</v>
+        <v>2776.74</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1297.86</v>
+        <v>1301.94</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>779.88</v>
+        <v>782.33</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>5296.11</v>
+        <v>5312.77</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1658.09</v>
+        <v>1664.96</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1291.03</v>
+        <v>1296.38</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1895.05</v>
+        <v>1902.91</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6228.13</v>
+        <v>6253.94</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>809.74</v>
+        <v>813.09</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1183.22</v>
+        <v>1188.13</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1308.63</v>
+        <v>1314.05</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2793.59</v>
+        <v>2805.17</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3753.48</v>
+        <v>3769.04</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1129.13</v>
+        <v>1133.81</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1429.1</v>
+        <v>1435.03</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5946.69</v>
+        <v>5971.34</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2292.78</v>
+        <v>2302.28</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1085.78</v>
+        <v>1090.28</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>926.98</v>
+        <v>928.91</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3204.52</v>
+        <v>3211.15</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6410.22</v>
+        <v>6382.68</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>15476.25</v>
+        <v>15409.77</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>4815.7</v>
+        <v>4795.01</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>887.37</v>
+        <v>883.5599999999999</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2918.02</v>
+        <v>2905.48</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>10211.81</v>
+        <v>10167.94</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3124.54</v>
+        <v>3105.82</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3124.54</v>
+        <v>3105.82</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3124.54</v>
+        <v>3105.82</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1521.99</v>
+        <v>1501.3</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7267.92</v>
+        <v>7169.11</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>930.83</v>
+        <v>918.17</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>983.04</v>
+        <v>969.6799999999999</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2726.57</v>
+        <v>2703.31</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>985.14</v>
+        <v>976.73</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>19420.3</v>
+        <v>19524.88</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>8824.610000000001</v>
+        <v>8872.129999999999</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>792.6799999999999</v>
+        <v>796.95</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>889.27</v>
+        <v>894.0599999999999</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3178.54</v>
+        <v>3195.66</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2903.62</v>
+        <v>2936.1</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>842.0599999999999</v>
+        <v>851.47</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1190.64</v>
+        <v>1203.96</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1661.84</v>
+        <v>1680.42</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>803.66</v>
+        <v>812.64</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1327.22</v>
+        <v>1342.06</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2361.43</v>
+        <v>2387.84</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>885.14</v>
+        <v>895.04</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1887.25</v>
+        <v>1901.54</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>984.7</v>
+        <v>992.15</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3371.91</v>
+        <v>3397.45</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>3474.67</v>
+        <v>3487.84</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1929.35</v>
+        <v>1936.66</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>7440.46</v>
+        <v>7468.64</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1516.46</v>
+        <v>1522.21</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1114.19</v>
+        <v>1118.41</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1420.36</v>
+        <v>1425.74</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>5822.55</v>
+        <v>5844.61</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>828.17</v>
+        <v>831.3099999999999</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>3860.8</v>
+        <v>3897.48</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>5032.88</v>
+        <v>5070.37</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1054.33</v>
+        <v>1062.19</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>15121.63</v>
+        <v>15234.29</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>800.9400000000001</v>
+        <v>806.9</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>884.29</v>
+        <v>890.88</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3225.58</v>
+        <v>3249.61</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2469.59</v>
+        <v>2444.96</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>793.9299999999999</v>
+        <v>790.45</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1554.73</v>
+        <v>1547.92</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>5185.83</v>
+        <v>5163.1</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1678.2</v>
+        <v>1670.84</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1469.58</v>
+        <v>1463.14</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>850.92</v>
+        <v>847.1900000000001</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1026.15</v>
+        <v>1014.99</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>16179.37</v>
+        <v>16142.65</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7224.12</v>
+        <v>7207.72</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>856.13</v>
+        <v>854.1799999999999</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1322.74</v>
+        <v>1319.74</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1146.12</v>
+        <v>1143.52</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1559.64</v>
+        <v>1556.1</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2740.73</v>
+        <v>2733.96</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2761.51</v>
+        <v>2754.7</v>
       </c>
     </row>
     <row r="411">
@@ -25518,13 +25518,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2270.4</v>
+        <v>2281.56</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1079505-242-CM26</t>
+          <t>1079505-243-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K412" t="inlineStr"/>
@@ -25579,13 +25579,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>977.79</v>
+        <v>2397.09</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1079505-243-CM26</t>
+          <t>1079505-242-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K413" t="inlineStr"/>
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2385.37</v>
+        <v>982.6</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>788.75</v>
+        <v>791.37</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1740.39</v>
+        <v>1746.16</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>9652.360000000001</v>
+        <v>9684.379999999999</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>6155.22</v>
+        <v>6175.64</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1133.53</v>
+        <v>1137.14</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1712.24</v>
+        <v>1717.69</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4873.76</v>
+        <v>4889.28</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1667.12</v>
+        <v>1672.43</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1178.47</v>
+        <v>1184.73</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>857.5599999999999</v>
+        <v>862.12</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2282.44</v>
+        <v>2294.58</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>827.41</v>
+        <v>831.8099999999999</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>796.41</v>
+        <v>800.64</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1621.4</v>
+        <v>1630.02</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>1592.29</v>
+        <v>1615.08</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>830.61</v>
+        <v>840.35</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>906.04</v>
+        <v>921.36</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1812.63</v>
+        <v>1843.28</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2333.62</v>
+        <v>2373.09</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1098.04</v>
+        <v>1116.61</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>839.52</v>
+        <v>853.72</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>5455.49</v>
+        <v>5510.96</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1719.71</v>
+        <v>1735.84</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2248.85</v>
+        <v>2269.95</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>6959.63</v>
+        <v>7024.9</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>9603.33</v>
+        <v>9693.4</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>4954.92</v>
+        <v>5001.4</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2876.12</v>
+        <v>2854.3</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1600.7</v>
+        <v>1588.55</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1213.58</v>
+        <v>1193.08</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1457.83</v>
+        <v>1433.2</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>19296.77</v>
+        <v>19031.63</v>
       </c>
     </row>
     <row r="446">
@@ -27653,13 +27653,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>3897.23</v>
+        <v>3843.68</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>627786-110-CM26</t>
+          <t>627786-111-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -27699,12 +27699,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>COMERCIALIZACION Y DISTRIBUCION DE ALIMENTOS S &amp; F LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>76.193.972-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K447" t="inlineStr"/>
@@ -27714,13 +27714,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>6721.06</v>
+        <v>3056.87</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>627786-111-CM26</t>
+          <t>627786-110-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -27760,12 +27760,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COMERCIALIZACION Y DISTRIBUCION DE ALIMENTOS S &amp; F LIMITADA</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.193.972-6</t>
         </is>
       </c>
       <c r="K448" t="inlineStr"/>
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>3099.46</v>
+        <v>6628.71</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2892.23</v>
+        <v>2852.49</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>1068.52</v>
+        <v>1061.89</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>800.73</v>
+        <v>795.76</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>935.85</v>
+        <v>930.05</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1133.42</v>
+        <v>1126.39</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2629.36</v>
+        <v>2613.05</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>34329.75</v>
+        <v>34485.67</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1513.86</v>
+        <v>1520.73</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4777.73</v>
+        <v>4848.88</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>5365.09</v>
+        <v>5467.09</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1098.58</v>
+        <v>1119.46</v>
       </c>
     </row>
     <row r="460">
@@ -28507,13 +28507,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2999.52</v>
+        <v>3056.55</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>548238-91-CM26</t>
+          <t>548238-89-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -28553,12 +28553,12 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>FRIGORIFICO DE OSORNO S A</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>96.518.090-7</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K461" t="inlineStr"/>
@@ -28568,13 +28568,13 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3828.27</v>
+        <v>1001.62</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>548238-90-CM26</t>
+          <t>548238-91-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -28614,12 +28614,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>FRIGORIFICO DE OSORNO S A</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>96.518.090-7</t>
         </is>
       </c>
       <c r="K462" t="inlineStr"/>
@@ -28629,13 +28629,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1000.5</v>
+        <v>3854.7</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>548238-89-CM26</t>
+          <t>548238-90-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -28675,12 +28675,12 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K463" t="inlineStr"/>
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>994.75</v>
+        <v>1007.41</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>17659.82</v>
+        <v>17781.74</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2396.29</v>
+        <v>2412.83</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>9314.309999999999</v>
+        <v>9378.620000000001</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>803.11</v>
+        <v>800.99</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>3492.75</v>
+        <v>3483.51</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>3104.67</v>
+        <v>3096.46</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2309.44</v>
+        <v>2303.33</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2309.44</v>
+        <v>2303.33</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1590.46</v>
+        <v>1586.26</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>4607.12</v>
+        <v>4594.93</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>902.6</v>
+        <v>900.21</v>
       </c>
     </row>
     <row r="475">
@@ -29422,13 +29422,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1236.06</v>
+        <v>1219.6</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1660-540-CM26</t>
+          <t>1079505-342-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29453,12 +29453,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29468,12 +29468,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>ALIMENTOS MKP LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>78.048.707-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -29483,13 +29483,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>946.4400000000001</v>
+        <v>938.33</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1079505-342-CM26</t>
+          <t>1660-540-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29529,12 +29529,12 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ALIMENTOS MKP LIMITADA</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.048.707-0</t>
         </is>
       </c>
       <c r="K477" t="inlineStr"/>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>957.0700000000001</v>
+        <v>927.92</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1002.47</v>
+        <v>982.85</v>
       </c>
     </row>
     <row r="479">
@@ -29666,13 +29666,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1620.61</v>
+        <v>1588.89</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1346282-297-CM26</t>
+          <t>548238-99-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -29692,17 +29692,17 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29712,12 +29712,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>CASO Y CIA SAC</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>92.423.000-2</t>
         </is>
       </c>
       <c r="K480" t="inlineStr"/>
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>951.5</v>
+        <v>2107.5</v>
       </c>
     </row>
     <row r="481">
@@ -29788,13 +29788,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1790.03</v>
+        <v>1763.51</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>548238-99-CM26</t>
+          <t>1346282-297-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -29814,17 +29814,17 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29834,12 +29834,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>CASO Y CIA SAC</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>92.423.000-2</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K482" t="inlineStr"/>
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2139.19</v>
+        <v>937.4</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>11989.02</v>
+        <v>11742.63</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2900.26</v>
+        <v>2840.65</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>1527.81</v>
+        <v>1496.41</v>
       </c>
     </row>
     <row r="486">
@@ -30093,13 +30093,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1590.84</v>
+        <v>1558.15</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>1079505-353-CM26</t>
+          <t>1346282-298-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -30119,17 +30119,17 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30139,12 +30139,12 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEDERICO </t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>77.018.148-8</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K487" t="inlineStr"/>
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1560.45</v>
+        <v>792.33</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1346282-298-CM26</t>
+          <t>1079505-351-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -30185,12 +30185,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -30200,12 +30200,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>INVERSIONES LA REINA SPA</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.271.679-8</t>
         </is>
       </c>
       <c r="K488" t="inlineStr"/>
@@ -30215,13 +30215,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>784.87</v>
+        <v>1047.65</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1079505-351-CM26</t>
+          <t>1079505-352-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -30261,12 +30261,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>INVERSIONES LA REINA SPA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>76.271.679-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K489" t="inlineStr"/>
@@ -30276,13 +30276,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1037.79</v>
+        <v>1093.71</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>1079505-352-CM26</t>
+          <t>1079505-353-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -30322,12 +30322,12 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t xml:space="preserve">FEDERICO </t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>77.018.148-8</t>
         </is>
       </c>
       <c r="K490" t="inlineStr"/>
@@ -30337,13 +30337,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1083.42</v>
+        <v>1575.27</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5416-670-CM26</t>
+          <t>627786-129-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -30368,12 +30368,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K491" t="inlineStr"/>
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>814.12</v>
+        <v>10188.46</v>
       </c>
     </row>
     <row r="492">
@@ -30459,13 +30459,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>12146.3</v>
+        <v>12268.46</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>627786-129-CM26</t>
+          <t>5416-670-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -30490,12 +30490,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30505,12 +30505,12 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K493" t="inlineStr"/>
@@ -30520,13 +30520,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>10087.01</v>
+        <v>822.3099999999999</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1272615-52-CM26</t>
+          <t>1962-392-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -30546,17 +30546,17 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Hospital Provincial de Ovalle</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -30566,12 +30566,12 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>sociedad de nutricionistas nutrihouse ltda.</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>76.095.459-4</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K494" t="inlineStr"/>
@@ -30581,13 +30581,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>795.96</v>
+        <v>1884.75</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1962-383-CM26</t>
+          <t>1962-390-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -30627,12 +30627,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K495" t="inlineStr"/>
@@ -30642,13 +30642,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4684.3</v>
+        <v>1052.37</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1962-388-CM26</t>
+          <t>1962-389-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -30688,12 +30688,12 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>alimentos y frutos</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>96.557.910-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K496" t="inlineStr"/>
@@ -30703,13 +30703,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>1190.32</v>
+        <v>1358.68</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1962-389-CM26</t>
+          <t>1962-388-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -30749,12 +30749,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>alimentos y frutos</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.557.910-9</t>
         </is>
       </c>
       <c r="K497" t="inlineStr"/>
@@ -30764,13 +30764,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1345.21</v>
+        <v>1202.24</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1962-390-CM26</t>
+          <t>1962-383-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K498" t="inlineStr"/>
@@ -30825,13 +30825,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1041.93</v>
+        <v>4731.21</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1962-392-CM26</t>
+          <t>1272615-52-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -30851,17 +30851,17 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>Hospital Provincial de Ovalle</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -30871,12 +30871,12 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>sociedad de nutricionistas nutrihouse ltda.</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.095.459-4</t>
         </is>
       </c>
       <c r="K499" t="inlineStr"/>
@@ -30886,13 +30886,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1866.06</v>
+        <v>803.9299999999999</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1057439-4498-CM26</t>
+          <t>1962-391-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -30912,17 +30912,17 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -30932,12 +30932,12 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K500" t="inlineStr"/>
@@ -30947,13 +30947,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2159.15</v>
+        <v>1387.53</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1962-391-CM26</t>
+          <t>1057439-4498-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -30973,17 +30973,17 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -30993,12 +30993,12 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K501" t="inlineStr"/>
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1380.5</v>
+        <v>2170.15</v>
       </c>
     </row>
     <row r="502">
@@ -31069,13 +31069,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>4180.94</v>
+        <v>4202.25</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1962-404-CM26</t>
+          <t>1346282-300-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -31100,12 +31100,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31115,12 +31115,12 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Macro Food S.A.</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>96.733.580-0</t>
         </is>
       </c>
       <c r="K503" t="inlineStr"/>
@@ -31130,13 +31130,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>947.9299999999999</v>
+        <v>780.15</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1057439-4500-CM26</t>
+          <t>1346282-301-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -31156,17 +31156,17 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -31176,12 +31176,12 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>alimentos y frutos</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>96.557.910-9</t>
         </is>
       </c>
       <c r="K504" t="inlineStr"/>
@@ -31191,13 +31191,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>18724.99</v>
+        <v>775.66</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1962-399-CM26</t>
+          <t>1962-396-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -31237,12 +31237,12 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>FRIGORIFICO DE OSORNO S A</t>
+          <t xml:space="preserve">FRIO SUR ALIMENTOS DEL MAR S.A </t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>96.518.090-7</t>
+          <t>78.081.820-4</t>
         </is>
       </c>
       <c r="K505" t="inlineStr"/>
@@ -31252,13 +31252,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1634.53</v>
+        <v>1043.35</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>1962-400-CM26</t>
+          <t>1962-399-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>CARNES NUBLE S A</t>
+          <t>FRIGORIFICO DE OSORNO S A</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>96.518.070-2</t>
+          <t>96.518.090-7</t>
         </is>
       </c>
       <c r="K506" t="inlineStr"/>
@@ -31313,13 +31313,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>897.8200000000001</v>
+        <v>1640.89</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1346282-301-CM26</t>
+          <t>1057439-4500-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -31339,17 +31339,17 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -31359,12 +31359,12 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>alimentos y frutos</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>96.557.910-9</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K507" t="inlineStr"/>
@@ -31374,13 +31374,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>772.65</v>
+        <v>18797.88</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1346282-300-CM26</t>
+          <t>1962-400-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -31405,12 +31405,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -31420,12 +31420,12 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Macro Food S.A.</t>
+          <t>CARNES NUBLE S A</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>96.733.580-0</t>
+          <t>96.518.070-2</t>
         </is>
       </c>
       <c r="K508" t="inlineStr"/>
@@ -31435,13 +31435,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>777.12</v>
+        <v>901.3099999999999</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1962-396-CM26</t>
+          <t>1962-404-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -31481,12 +31481,12 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRIO SUR ALIMENTOS DEL MAR S.A </t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>78.081.820-4</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K509" t="inlineStr"/>
@@ -31496,13 +31496,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1039.3</v>
+        <v>951.62</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1079505-377-CM26</t>
+          <t>1962-406-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -31527,12 +31527,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>INVERSIONES LA REINA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>76.271.679-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K510" t="inlineStr"/>
@@ -31557,13 +31557,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>774.88</v>
+        <v>5034.74</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1962-397-CM26</t>
+          <t>548238-105-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -31583,17 +31583,17 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>SURLAT COMERCIAL S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>96.954.210-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K511" t="inlineStr"/>
@@ -31618,13 +31618,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1348.13</v>
+        <v>932.4</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1962-401-CM26</t>
+          <t>1962-407-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -31644,7 +31644,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -31664,12 +31664,12 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>SOPROLE</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>84.472.400-4</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K512" t="inlineStr"/>
@@ -31679,13 +31679,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1076.8</v>
+        <v>1117.92</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>548238-105-CM26</t>
+          <t>1962-397-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -31705,17 +31705,17 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -31725,12 +31725,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SURLAT COMERCIAL S.A.</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.954.210-2</t>
         </is>
       </c>
       <c r="K513" t="inlineStr"/>
@@ -31740,13 +31740,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>937.15</v>
+        <v>1341.3</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1962-406-CM26</t>
+          <t>1962-401-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -31786,12 +31786,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOPROLE</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>84.472.400-4</t>
         </is>
       </c>
       <c r="K514" t="inlineStr"/>
@@ -31801,13 +31801,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5060.38</v>
+        <v>1071.35</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1962-407-CM26</t>
+          <t>1079505-377-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -31832,12 +31832,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -31847,12 +31847,12 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>INVERSIONES LA REINA SPA</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>76.271.679-8</t>
         </is>
       </c>
       <c r="K515" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1123.61</v>
+        <v>770.96</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1881.69</v>
+        <v>1885.7</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>909.98</v>
+        <v>911.92</v>
       </c>
     </row>
     <row r="518">
@@ -32045,13 +32045,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3230.07</v>
+        <v>3237.48</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1079505-404-CM26</t>
+          <t>1346282-311-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -32071,17 +32071,17 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32091,12 +32091,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>MANANTIAL S A</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>96.711.590-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K519" t="inlineStr"/>
@@ -32106,13 +32106,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>848.12</v>
+        <v>3060.75</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>1346282-315-CM26</t>
+          <t>1079505-404-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -32132,17 +32132,17 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32152,12 +32152,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>MANANTIAL S A</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>96.711.590-8</t>
         </is>
       </c>
       <c r="K520" t="inlineStr"/>
@@ -32167,13 +32167,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>2128.88</v>
+        <v>853.8</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1346282-311-CM26</t>
+          <t>1346282-315-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -32213,12 +32213,12 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K521" t="inlineStr"/>
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3040.39</v>
+        <v>2143.13</v>
       </c>
     </row>
     <row r="522">
@@ -32289,13 +32289,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>779.48</v>
+        <v>784.6900000000001</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1346282-308-CM26</t>
+          <t>1346282-309-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -32335,12 +32335,12 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEDERICO </t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>77.018.148-8</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K523" t="inlineStr"/>
@@ -32350,13 +32350,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1088.27</v>
+        <v>1058.41</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1346282-307-CM26</t>
+          <t>1346282-308-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -32411,13 +32411,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>5831</v>
+        <v>1095.55</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1346282-309-CM26</t>
+          <t>1346282-307-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -32457,12 +32457,12 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t xml:space="preserve">FEDERICO </t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>77.018.148-8</t>
         </is>
       </c>
       <c r="K525" t="inlineStr"/>
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1051.38</v>
+        <v>5870.03</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1021.65</v>
+        <v>1028.8</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1270.84</v>
+        <v>1279.73</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>965.96</v>
+        <v>972.72</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1831.28</v>
+        <v>1844.1</v>
       </c>
     </row>
     <row r="530">
@@ -32777,13 +32777,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>818.9299999999999</v>
+        <v>824.66</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>3532-101-CM26</t>
+          <t>3532-109-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -32823,12 +32823,12 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA OSCAR HUGO CONTRERAS PÉREZ E.I.R.L.</t>
+          <t>CARNES NUBLE S A</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>77.275.835-9</t>
+          <t>96.518.070-2</t>
         </is>
       </c>
       <c r="K531" t="inlineStr"/>
@@ -32838,13 +32838,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1051.7</v>
+        <v>1910.21</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>3532-109-CM26</t>
+          <t>3532-101-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -32884,12 +32884,12 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>CARNES NUBLE S A</t>
+          <t>COMERCIALIZADORA OSCAR HUGO CONTRERAS PÉREZ E.I.R.L.</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>96.518.070-2</t>
+          <t>77.275.835-9</t>
         </is>
       </c>
       <c r="K532" t="inlineStr"/>
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1914.38</v>
+        <v>1049.41</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1080.85</v>
+        <v>1078.68</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>788.05</v>
+        <v>786.47</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1409.44</v>
+        <v>1406.61</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1845.68</v>
+        <v>1824.2</v>
       </c>
     </row>
     <row r="537">
@@ -33204,13 +33204,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1096.35</v>
+        <v>1083.6</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1346282-331-CM26</t>
+          <t>3712-489-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -33235,12 +33235,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K538" t="inlineStr"/>
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>835.88</v>
+        <v>772.72</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>3712-489-CM26</t>
+          <t>1346282-331-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -33296,12 +33296,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33311,12 +33311,12 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K539" t="inlineStr"/>
@@ -33326,13 +33326,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>777.03</v>
+        <v>831.24</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>1079505-434-CM26</t>
+          <t>1962-462-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -33352,17 +33352,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -33372,12 +33372,12 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>MANANTIAL S A</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>96.711.590-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K540" t="inlineStr"/>
@@ -33387,13 +33387,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1650.54</v>
+        <v>1477.31</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1962-462-CM26</t>
+          <t>1079505-434-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -33413,17 +33413,17 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -33433,12 +33433,12 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>MANANTIAL S A</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>96.711.590-8</t>
         </is>
       </c>
       <c r="K541" t="inlineStr"/>
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1484.61</v>
+        <v>1642.42</v>
       </c>
     </row>
     <row r="542">
@@ -33509,13 +33509,13 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>4380.27</v>
+        <v>4358.73</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1962-464-CM26</t>
+          <t>3532-115-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -33540,12 +33540,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -33555,12 +33555,12 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
+          <t>COMERCIALIZADORA OSCAR HUGO CONTRERAS PÉREZ E.I.R.L.</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>77.965.620-9</t>
+          <t>77.275.835-9</t>
         </is>
       </c>
       <c r="K543" t="inlineStr"/>
@@ -33570,13 +33570,13 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1497.29</v>
+        <v>2826.4</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1962-465-CM26</t>
+          <t>3532-116-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -33596,17 +33596,17 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33616,12 +33616,12 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K544" t="inlineStr"/>
@@ -33631,13 +33631,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1867.08</v>
+        <v>4472.36</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>3532-115-CM26</t>
+          <t>1962-464-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -33677,12 +33677,12 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA OSCAR HUGO CONTRERAS PÉREZ E.I.R.L.</t>
+          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>77.275.835-9</t>
+          <t>77.965.620-9</t>
         </is>
       </c>
       <c r="K545" t="inlineStr"/>
@@ -33692,13 +33692,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>2807.61</v>
+        <v>1507.31</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>3532-116-CM26</t>
+          <t>1962-465-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -33718,17 +33718,17 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K546" t="inlineStr"/>
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>4442.62</v>
+        <v>1879.58</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,251 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>771.1799999999999</v>
+        <v>776.35</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>1057438-204-CM26</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>COMERCIAL SOLO FRESCO SA</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>76.102.347-0</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="n">
+        <v>2946.15</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>1272615-66-CM26</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="n">
+        <v>4751.2</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>1346282-343-CM26</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>BIDFOOD CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>76.111.152-3</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="n">
+        <v>1175.6</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>1272615-82-CM26</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>sociedad de nutricionistas nutrihouse ltda.</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>76.095.459-4</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="n">
+        <v>2308.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/alimentos/coquimbo.xlsx
+++ b/docs/oc-regiones/alimentos/coquimbo.xlsx
@@ -623,7 +623,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1420,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3152,7 +3160,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4461,7 +4473,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6388,7 +6404,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8323,7 +8343,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8945,7 +8969,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9933,7 +9961,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10933,7 +10965,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11681,7 +11717,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11868,7 +11908,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11929,7 +11973,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12868,7 +12916,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +13737,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14002,7 +14058,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14063,7 +14123,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14124,7 +14188,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14498,7 +14566,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15189,7 +15261,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15441,7 +15517,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16063,7 +16143,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16372,7 +16456,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16620,7 +16708,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16864,7 +16956,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17356,7 +17452,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17791,7 +17891,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18043,7 +18147,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18291,7 +18399,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18604,7 +18716,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19482,7 +19598,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19990,7 +20110,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20051,7 +20175,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21563,7 +21691,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22120,7 +22252,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22181,7 +22317,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22933,7 +23073,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +23585,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24628,7 +24776,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25567,7 +25719,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26461,7 +26617,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27034,7 +27194,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27843,7 +28007,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27904,7 +28072,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28652,7 +28824,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29477,7 +29653,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30034,7 +30214,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30794,7 +30978,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31595,7 +31783,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32034,7 +32226,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +32356,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32717,7 +32917,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32965,7 +33169,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33339,7 +33547,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33725,7 +33937,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34611,7 +34827,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35420,7 +35640,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36233,7 +36457,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36542,7 +36770,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37107,7 +37339,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38119,7 +38355,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38562,7 +38802,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39066,7 +39310,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39371,7 +39619,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40322,7 +40574,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41834,7 +42090,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42204,7 +42464,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42265,7 +42529,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43956,7 +44224,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44147,7 +44419,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45887,7 +46163,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46139,7 +46419,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46521,7 +46805,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47078,7 +47366,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47976,7 +48268,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48362,7 +48658,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48549,7 +48849,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49171,7 +49475,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49675,7 +49983,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50041,7 +50353,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51065,7 +51381,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52402,7 +52722,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52715,7 +53039,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52902,7 +53230,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53024,7 +53356,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53390,7 +53726,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54020,7 +54360,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55097,7 +55441,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56621,7 +56969,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56682,7 +57034,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56934,7 +57290,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57060,7 +57420,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57247,7 +57611,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57308,7 +57676,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58178,7 +58550,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59499,7 +59875,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60442,7 +60822,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L958" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60763,7 +61147,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60824,7 +61212,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L964" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61641,7 +62033,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61702,7 +62098,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L978" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63641,7 +64041,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1009" t="inlineStr"/>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1009" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63893,7 +64297,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64982,7 +65390,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1030" t="inlineStr"/>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1030" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66876,7 +67288,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1060" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68059,7 +68475,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1079" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68120,7 +68540,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1080" t="inlineStr"/>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1080" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68494,7 +68918,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1086" t="inlineStr"/>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1086" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68876,7 +69304,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1092" t="inlineStr"/>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1092" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69307,7 +69739,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1099" t="inlineStr"/>
+      <c r="K1099" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1099" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70189,7 +70625,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1113" t="inlineStr"/>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70872,7 +71312,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1124" t="inlineStr"/>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -71498,7 +71942,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1134" t="inlineStr"/>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -72250,7 +72698,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1146" t="inlineStr"/>
+      <c r="K1146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -72433,7 +72885,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1149" t="inlineStr"/>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -73445,7 +73901,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1165" t="inlineStr"/>
+      <c r="K1165" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -73819,7 +74279,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1171" t="inlineStr"/>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -74063,7 +74527,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1175" t="inlineStr"/>
+      <c r="K1175" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -74372,7 +74840,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1180" t="inlineStr"/>
+      <c r="K1180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -74559,7 +75031,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1183" t="inlineStr"/>
+      <c r="K1183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -74681,7 +75157,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1185" t="inlineStr"/>
+      <c r="K1185" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -75246,7 +75726,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1194" t="inlineStr"/>
+      <c r="K1194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -76120,7 +76604,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1208" t="inlineStr"/>
+      <c r="K1208" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -76925,7 +77413,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1221" t="inlineStr"/>
+      <c r="K1221" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -77368,7 +77860,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1228" t="inlineStr"/>
+      <c r="K1228" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1228" t="inlineStr">
         <is>
           <t>USD</t>
